--- a/Result/profitability/5410.xlsx
+++ b/Result/profitability/5410.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.31</v>
       </c>
       <c r="M2" t="n">
-        <v>0.62375</v>
+        <v>0.6975</v>
       </c>
       <c r="N2" t="n">
-        <v>18.7525</v>
+        <v>18.64875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.72</v>
       </c>
       <c r="M3" t="n">
-        <v>0.49125</v>
+        <v>0.5437500000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>20.31125</v>
+        <v>20.3475</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.1</v>
       </c>
       <c r="M4" t="n">
-        <v>0.415</v>
+        <v>0.45</v>
       </c>
       <c r="N4" t="n">
-        <v>21.645</v>
+        <v>21.615</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.5</v>
       </c>
       <c r="M5" t="n">
-        <v>0.27125</v>
+        <v>0.3</v>
       </c>
       <c r="N5" t="n">
-        <v>24.18375</v>
+        <v>22.95875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,13 +1137,13 @@
         <v>0.24</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2137500000000001</v>
+        <v>0.275</v>
       </c>
       <c r="N6" t="n">
-        <v>25.54875</v>
+        <v>25.68125</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
@@ -1155,7 +1155,7 @@
         <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.08</v>
       </c>
       <c r="M7" t="n">
-        <v>0.14875</v>
+        <v>0.195</v>
       </c>
       <c r="N7" t="n">
-        <v>27.6775</v>
+        <v>26.615</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.22</v>
       </c>
       <c r="M8" t="n">
-        <v>0.05125000000000001</v>
+        <v>-0.01749999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>27.7775</v>
+        <v>27.07625</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1518,7 +1518,7 @@
         <v>0.55</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.06499999999999997</v>
+        <v>-0.065</v>
       </c>
       <c r="N9" t="n">
         <v>27.98</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5410</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1698</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1456</v>
+      </c>
+      <c r="E75" t="n">
+        <v>242</v>
+      </c>
+      <c r="F75" t="n">
+        <v>14.23</v>
+      </c>
+      <c r="G75" t="n">
+        <v>70</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>4.14%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>36</v>
+      </c>
+      <c r="J75" t="n">
+        <v>106</v>
+      </c>
+      <c r="K75" t="n">
+        <v>86</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.70125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>17.18375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.5499999999999999</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.3716216216216216</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-5.609999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.2827620967741935</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.2300000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.3285714285714287</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-9.800000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.4078235538909696</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
